--- a/artfynd/A 46828-2025 artfynd.xlsx
+++ b/artfynd/A 46828-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>89601378</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468033.7887503285</v>
+        <v>468034</v>
       </c>
       <c r="R2" t="n">
-        <v>7094831.881803993</v>
+        <v>7094832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89601365</v>
+        <v>89601368</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468028.0321802973</v>
+        <v>468000</v>
       </c>
       <c r="R3" t="n">
-        <v>7094827.988197072</v>
+        <v>7094833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,6 +875,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89601365</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brinnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468028</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7094828</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
